--- a/artfynd/A 34560-2020 artfynd.xlsx
+++ b/artfynd/A 34560-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34560-2020 artfynd.xlsx
+++ b/artfynd/A 34560-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1707,6 +1707,129 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126343455</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57606</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102110</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fjällvråk</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Buteo lagopus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hästberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>711474</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7398503</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Rickard Nordlund</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Rickard Nordlund</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34560-2020 artfynd.xlsx
+++ b/artfynd/A 34560-2020 artfynd.xlsx
@@ -1712,7 +1712,7 @@
         <v>126343455</v>
       </c>
       <c r="B10" t="n">
-        <v>57606</v>
+        <v>57607</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
